--- a/server/sample_invoices.xlsx
+++ b/server/sample_invoices.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="172">
   <si>
     <t>Invoice Number</t>
   </si>
@@ -56,400 +56,397 @@
     <t>INV-000001</t>
   </si>
   <si>
-    <t>Acme Corporation</t>
-  </si>
-  <si>
-    <t>Acme Corp Pte Ltd</t>
-  </si>
-  <si>
-    <t>billing@acmecorp.sg</t>
+    <t>Luxe Hair Studio</t>
+  </si>
+  <si>
+    <t>Luxe Hair Studio Pte Ltd</t>
+  </si>
+  <si>
+    <t>bookings@luxehairstudio.sg</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Includes all applicable taxes.</t>
+  </si>
+  <si>
+    <t>INV-000002</t>
+  </si>
+  <si>
+    <t>The Nail Artistry</t>
+  </si>
+  <si>
+    <t>The Nail Artistry Pte Ltd</t>
+  </si>
+  <si>
+    <t>hello@thenailartistry.sg</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>Payment due within 30 days.</t>
+  </si>
+  <si>
+    <t>INV-000003</t>
+  </si>
+  <si>
+    <t>Serenity Spa &amp; Wellness</t>
+  </si>
+  <si>
+    <t>Serenity Spa &amp; Wellness Pte Ltd</t>
+  </si>
+  <si>
+    <t>reservations@serenityspa.sg</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>For queries, contact finance@paynivo.com.</t>
+  </si>
+  <si>
+    <t>INV-000004</t>
+  </si>
+  <si>
+    <t>Glow Aesthetics Clinic</t>
+  </si>
+  <si>
+    <t>Glow Aesthetics Clinic Pte Ltd</t>
+  </si>
+  <si>
+    <t>appointments@glowaesthetics.sg</t>
   </si>
   <si>
     <t>2026-07-13</t>
   </si>
   <si>
+    <t>INV-000005</t>
+  </si>
+  <si>
+    <t>Brow &amp; Lash Bar</t>
+  </si>
+  <si>
+    <t>Brow &amp; Lash Bar Pte Ltd</t>
+  </si>
+  <si>
+    <t>info@browlashbar.sg</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>INV-000006</t>
+  </si>
+  <si>
+    <t>KBeauty Haven</t>
+  </si>
+  <si>
+    <t>KBeauty Haven Pte Ltd</t>
+  </si>
+  <si>
+    <t>hello@kbeautyhaven.sg</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>Late payment incurs 2% monthly interest.</t>
+  </si>
+  <si>
+    <t>INV-000007</t>
+  </si>
+  <si>
+    <t>Zen Reflexology Centre</t>
+  </si>
+  <si>
+    <t>Zen Reflexology Centre Pte Ltd</t>
+  </si>
+  <si>
+    <t>bookings@zenreflexology.sg</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>Sent</t>
+  </si>
+  <si>
+    <t>INV-000008</t>
+  </si>
+  <si>
+    <t>Prestige Barbers</t>
+  </si>
+  <si>
+    <t>Prestige Barbers Pte Ltd</t>
+  </si>
+  <si>
+    <t>appointments@prestigebarbers.sg</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>INV-000009</t>
+  </si>
+  <si>
+    <t>Skin Lab Express</t>
+  </si>
+  <si>
+    <t>Skin Lab Express Pte Ltd</t>
+  </si>
+  <si>
+    <t>info@skinlabexpress.sg</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>INV-000010</t>
+  </si>
+  <si>
+    <t>Orchid Beauty Lounge</t>
+  </si>
+  <si>
+    <t>Orchid Beauty Lounge Pte Ltd</t>
+  </si>
+  <si>
+    <t>bookings@orchidbeauty.sg</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>Recurring monthly service charge.</t>
+  </si>
+  <si>
+    <t>INV-000011</t>
+  </si>
+  <si>
+    <t>The Waxing Boutique</t>
+  </si>
+  <si>
+    <t>The Waxing Boutique Pte Ltd</t>
+  </si>
+  <si>
+    <t>hello@waxingboutique.sg</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>Thank you for choosing our services.</t>
+  </si>
+  <si>
+    <t>INV-000012</t>
+  </si>
+  <si>
+    <t>Radiance Medi-Spa</t>
+  </si>
+  <si>
+    <t>Radiance Medi-Spa Pte Ltd</t>
+  </si>
+  <si>
+    <t>info@radiancespa.sg</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>Please reference invoice number in payment.</t>
+  </si>
+  <si>
+    <t>INV-000013</t>
+  </si>
+  <si>
+    <t>Aura Hair &amp; Beauty</t>
+  </si>
+  <si>
+    <t>Aura Hair &amp; Beauty Pte Ltd</t>
+  </si>
+  <si>
+    <t>bookings@aurahairbeauty.sg</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>Viewed</t>
+  </si>
+  <si>
+    <t>INV-000014</t>
+  </si>
+  <si>
+    <t>Bliss Nail Studio</t>
+  </si>
+  <si>
+    <t>Bliss Nail Studio Pte Ltd</t>
+  </si>
+  <si>
+    <t>hello@blissnails.sg</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>INV-000015</t>
+  </si>
+  <si>
+    <t>Rejuve Wellness Clinic</t>
+  </si>
+  <si>
+    <t>Rejuve Wellness Clinic Pte Ltd</t>
+  </si>
+  <si>
+    <t>appointments@rejuveclinic.sg</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>INV-000016</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
     <t>2026-08-02</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>Late payment incurs 2% monthly interest.</t>
-  </si>
-  <si>
-    <t>INV-000002</t>
-  </si>
-  <si>
-    <t>TechWave Solutions</t>
-  </si>
-  <si>
-    <t>TechWave Solutions Pte Ltd</t>
-  </si>
-  <si>
-    <t>accounts@techwave.sg</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>Please reference invoice number in payment.</t>
-  </si>
-  <si>
-    <t>INV-000003</t>
-  </si>
-  <si>
-    <t>Marina Bay Trading</t>
-  </si>
-  <si>
-    <t>Marina Bay Trading Co</t>
-  </si>
-  <si>
-    <t>finance@marinabay.sg</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>Recurring monthly service charge.</t>
-  </si>
-  <si>
-    <t>INV-000004</t>
-  </si>
-  <si>
-    <t>Sunrise Digital</t>
-  </si>
-  <si>
-    <t>Sunrise Digital Pte Ltd</t>
-  </si>
-  <si>
-    <t>payment@sunrisedigital.sg</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>INV-000005</t>
-  </si>
-  <si>
-    <t>Pacific Ventures</t>
-  </si>
-  <si>
-    <t>Pacific Ventures Holdings</t>
-  </si>
-  <si>
-    <t>ap@pacificventures.sg</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>For queries, contact finance@paynivo.com.</t>
-  </si>
-  <si>
-    <t>INV-000006</t>
-  </si>
-  <si>
-    <t>GreenLeaf Consulting</t>
-  </si>
-  <si>
-    <t>GreenLeaf Consulting Group</t>
-  </si>
-  <si>
-    <t>invoices@greenleaf.sg</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>Includes all applicable taxes.</t>
-  </si>
-  <si>
-    <t>INV-000007</t>
-  </si>
-  <si>
-    <t>CloudNine Systems</t>
-  </si>
-  <si>
-    <t>CloudNine Systems Pte Ltd</t>
-  </si>
-  <si>
-    <t>billing@cloudnine.sg</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>Sent</t>
-  </si>
-  <si>
-    <t>Thank you for choosing our services.</t>
-  </si>
-  <si>
-    <t>INV-000008</t>
-  </si>
-  <si>
-    <t>Diamond Electronics</t>
-  </si>
-  <si>
-    <t>Diamond Electronics Trading</t>
-  </si>
-  <si>
-    <t>accounts@diamondel.sg</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>INV-000009</t>
-  </si>
-  <si>
-    <t>Golden Gate Logistics</t>
-  </si>
-  <si>
-    <t>Golden Gate Logistics Pte Ltd</t>
-  </si>
-  <si>
-    <t>finance@gglogistics.sg</t>
+    <t>Volume discount applied.</t>
+  </si>
+  <si>
+    <t>INV-000017</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>INV-000018</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>INV-000019</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Auto-generated invoice.</t>
+  </si>
+  <si>
+    <t>INV-000020</t>
+  </si>
+  <si>
+    <t>INV-000021</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>INV-000022</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
   </si>
   <si>
     <t>2026-06-30</t>
   </si>
   <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>INV-000010</t>
-  </si>
-  <si>
-    <t>Stellar Marketing</t>
-  </si>
-  <si>
-    <t>Stellar Marketing Agency</t>
-  </si>
-  <si>
-    <t>payments@stellarmarketing.sg</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>Payment due within 30 days.</t>
-  </si>
-  <si>
-    <t>INV-000011</t>
-  </si>
-  <si>
-    <t>BluePeak Software</t>
-  </si>
-  <si>
-    <t>BluePeak Software Pte Ltd</t>
-  </si>
-  <si>
-    <t>ar@bluepeaksw.sg</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>Volume discount applied.</t>
-  </si>
-  <si>
-    <t>INV-000012</t>
-  </si>
-  <si>
-    <t>Orchid Healthcare</t>
-  </si>
-  <si>
-    <t>Orchid Healthcare Services</t>
-  </si>
-  <si>
-    <t>billing@orchidhc.sg</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>INV-000013</t>
-  </si>
-  <si>
-    <t>Zenith Engineering</t>
-  </si>
-  <si>
-    <t>Zenith Engineering Works</t>
-  </si>
-  <si>
-    <t>accounts@zenitheng.sg</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>Viewed</t>
+    <t>INV-000023</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>INV-000024</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>INV-000025</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>Overdue</t>
+  </si>
+  <si>
+    <t>INV-000026</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>INV-000027</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>INV-000028</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>INV-000029</t>
   </si>
   <si>
     <t>Net 30 payment terms.</t>
   </si>
   <si>
-    <t>INV-000014</t>
-  </si>
-  <si>
-    <t>Coral Bay Restaurants</t>
-  </si>
-  <si>
-    <t>Coral Bay F&amp;B Group</t>
-  </si>
-  <si>
-    <t>finance@coralbay.sg</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>INV-000015</t>
-  </si>
-  <si>
-    <t>Atlas Security</t>
-  </si>
-  <si>
-    <t>Atlas Security Solutions</t>
-  </si>
-  <si>
-    <t>invoices@atlassec.sg</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>INV-000016</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>INV-000017</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>INV-000018</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>INV-000019</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>Auto-generated invoice.</t>
-  </si>
-  <si>
-    <t>INV-000020</t>
-  </si>
-  <si>
-    <t>INV-000021</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>INV-000022</t>
-  </si>
-  <si>
-    <t>2026-07-18</t>
-  </si>
-  <si>
-    <t>INV-000023</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>INV-000024</t>
-  </si>
-  <si>
-    <t>INV-000025</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>Overdue</t>
-  </si>
-  <si>
-    <t>INV-000026</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>INV-000027</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>INV-000028</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>INV-000029</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
     <t>INV-000030</t>
   </si>
   <si>
-    <t>2026-04-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
+    <t>2026-05-01</t>
   </si>
   <si>
     <t>Description</t>
@@ -461,76 +458,76 @@
     <t>Unit Price</t>
   </si>
   <si>
-    <t>Video Production Services</t>
-  </si>
-  <si>
-    <t>Software License Renewal</t>
-  </si>
-  <si>
-    <t>IT Support &amp; Maintenance (Monthly)</t>
-  </si>
-  <si>
-    <t>Hosting Services (Annual)</t>
-  </si>
-  <si>
-    <t>Domain Registration &amp; DNS Setup</t>
-  </si>
-  <si>
-    <t>Database Migration Services</t>
-  </si>
-  <si>
-    <t>Security Audit &amp; Penetration Testing</t>
-  </si>
-  <si>
-    <t>Email Marketing Campaign</t>
-  </si>
-  <si>
-    <t>Performance Optimization</t>
-  </si>
-  <si>
-    <t>Mobile App Development</t>
-  </si>
-  <si>
-    <t>Server Administration Services</t>
-  </si>
-  <si>
-    <t>UI/UX Design Consultation</t>
-  </si>
-  <si>
-    <t>Social Media Management</t>
-  </si>
-  <si>
-    <t>Network Configuration &amp; Setup</t>
-  </si>
-  <si>
-    <t>SEO Optimization Package</t>
-  </si>
-  <si>
-    <t>Cloud Infrastructure Setup</t>
-  </si>
-  <si>
-    <t>Data Analytics Dashboard Setup</t>
-  </si>
-  <si>
-    <t>Disaster Recovery Planning</t>
-  </si>
-  <si>
-    <t>API Integration Development</t>
-  </si>
-  <si>
-    <t>Custom Report Development</t>
-  </si>
-  <si>
-    <t>Technical Documentation</t>
-  </si>
-  <si>
-    <t>Training &amp; Onboarding Session</t>
-  </si>
-  <si>
-    <t>Web Development Services</t>
-  </si>
-  <si>
-    <t>Content Management System Setup</t>
+    <t>Eyebrow Embroidery</t>
+  </si>
+  <si>
+    <t>Chemical Peel Session</t>
+  </si>
+  <si>
+    <t>Scalp Treatment &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Nail Art Design Package</t>
+  </si>
+  <si>
+    <t>Facial Extraction &amp; Treatment</t>
+  </si>
+  <si>
+    <t>LED Light Therapy</t>
+  </si>
+  <si>
+    <t>Digital Perm</t>
+  </si>
+  <si>
+    <t>Hot Stone Therapy</t>
+  </si>
+  <si>
+    <t>Full Body Massage (90 min)</t>
+  </si>
+  <si>
+    <t>Eyelash Extensions (Full Set)</t>
+  </si>
+  <si>
+    <t>Full Leg Waxing</t>
+  </si>
+  <si>
+    <t>Underarm Waxing</t>
+  </si>
+  <si>
+    <t>Balayage Hair Coloring</t>
+  </si>
+  <si>
+    <t>Gel Manicure Session</t>
+  </si>
+  <si>
+    <t>Lash Lift &amp; Tint</t>
+  </si>
+  <si>
+    <t>Brazilian Waxing</t>
+  </si>
+  <si>
+    <t>Men's Grooming Package</t>
+  </si>
+  <si>
+    <t>Hair Extensions Installation</t>
+  </si>
+  <si>
+    <t>Classic Pedicure &amp; Foot Spa</t>
+  </si>
+  <si>
+    <t>Anti-Aging Collagen Mask</t>
+  </si>
+  <si>
+    <t>Keratin Smoothing Treatment</t>
+  </si>
+  <si>
+    <t>Microdermabrasion</t>
+  </si>
+  <si>
+    <t>Hair Rebonding</t>
+  </si>
+  <si>
+    <t>Hydrafacial Treatment</t>
   </si>
 </sst>
 </file>
@@ -993,16 +990,16 @@
         <v>20</v>
       </c>
       <c r="I2">
-        <v>20326.859999999997</v>
+        <v>87859.68</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>7907.37</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>7028.77</v>
       </c>
       <c r="L2">
-        <v>20326.86</v>
+        <v>88738.28</v>
       </c>
       <c r="M2" t="s">
         <v>21</v>
@@ -1025,7 +1022,7 @@
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1034,39 +1031,39 @@
         <v>20</v>
       </c>
       <c r="I3">
-        <v>60936.7</v>
+        <v>67449.40999999999</v>
       </c>
       <c r="J3">
-        <v>4265.57</v>
+        <v>5395.95</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>65202.27</v>
+        <v>72845.36</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -1075,39 +1072,39 @@
         <v>20</v>
       </c>
       <c r="I4">
-        <v>44896.64000000001</v>
+        <v>38986.51</v>
       </c>
       <c r="J4">
-        <v>4040.7</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>3591.73</v>
+        <v>2339.19</v>
       </c>
       <c r="L4">
-        <v>45345.61</v>
+        <v>36647.32</v>
       </c>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
         <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>39</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1116,39 +1113,39 @@
         <v>20</v>
       </c>
       <c r="I5">
-        <v>57417.46</v>
+        <v>23088.97</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1616.23</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>57417.46</v>
+        <v>24705.2</v>
       </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
         <v>19</v>
@@ -1157,36 +1154,36 @@
         <v>20</v>
       </c>
       <c r="I6">
-        <v>60866.83999999999</v>
+        <v>44686.61</v>
       </c>
       <c r="J6">
-        <v>4260.68</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>65127.52</v>
+        <v>44686.61</v>
       </c>
       <c r="M6" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>51</v>
@@ -1198,16 +1195,16 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <v>9753.74</v>
+        <v>52955.299999999996</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>4236.42</v>
       </c>
       <c r="K7">
-        <v>877.84</v>
+        <v>3706.87</v>
       </c>
       <c r="L7">
-        <v>8875.9</v>
+        <v>53484.85</v>
       </c>
       <c r="M7" t="s">
         <v>52</v>
@@ -1227,364 +1224,364 @@
         <v>56</v>
       </c>
       <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8">
-        <v>67814.98999999999</v>
+        <v>35826.86</v>
       </c>
       <c r="J8">
-        <v>6103.35</v>
+        <v>3224.42</v>
       </c>
       <c r="K8">
-        <v>2712.6</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>71205.74</v>
+        <v>39051.28</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>61</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s">
         <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>9936.2</v>
+        <v>17608.14</v>
       </c>
       <c r="J9">
-        <v>794.9</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>10731.1</v>
+        <v>17608.14</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>67</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>68</v>
       </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" t="s">
-        <v>70</v>
-      </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I10">
-        <v>17718.78</v>
+        <v>57815.42999999999</v>
       </c>
       <c r="J10">
-        <v>1594.69</v>
+        <v>5203.39</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>19313.47</v>
+        <v>63018.82</v>
       </c>
       <c r="M10" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
         <v>72</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>73</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" t="s">
-        <v>76</v>
       </c>
       <c r="G11" t="s">
         <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I11">
-        <v>25050.02</v>
+        <v>6836</v>
       </c>
       <c r="J11">
-        <v>1753.5</v>
+        <v>478.52</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>26803.52</v>
+        <v>7314.52</v>
       </c>
       <c r="M11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
         <v>78</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>79</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>80</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>82</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I12">
-        <v>10274.06</v>
+        <v>34409.49</v>
       </c>
       <c r="J12">
-        <v>924.67</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>11198.73</v>
+        <v>34409.49</v>
       </c>
       <c r="M12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
         <v>84</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>85</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>86</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
         <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" t="s">
-        <v>89</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I13">
-        <v>95954.62999999999</v>
+        <v>11190.48</v>
       </c>
       <c r="J13">
-        <v>6716.82</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1119.05</v>
       </c>
       <c r="L13">
-        <v>102671.45</v>
+        <v>10071.43</v>
       </c>
       <c r="M13" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
         <v>90</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>91</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>92</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s">
         <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I14">
-        <v>13120.91</v>
+        <v>24941.36</v>
       </c>
       <c r="J14">
-        <v>918.46</v>
+        <v>2244.72</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>14039.37</v>
+        <v>27186.08</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>98</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>99</v>
       </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>101</v>
-      </c>
       <c r="F15" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15">
-        <v>18095.61</v>
+        <v>46951.5</v>
       </c>
       <c r="J15">
-        <v>1447.65</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>904.78</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>18638.48</v>
+        <v>46951.5</v>
       </c>
       <c r="M15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
         <v>103</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E16" t="s">
         <v>104</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" t="s">
-        <v>107</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16">
-        <v>77157.48000000001</v>
+        <v>54940.57</v>
       </c>
       <c r="J16">
-        <v>6944.17</v>
+        <v>4395.25</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>84101.65</v>
+        <v>59335.82</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -1596,31 +1593,31 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I17">
-        <v>8096.55</v>
+        <v>84500.76999999999</v>
       </c>
       <c r="J17">
-        <v>647.72</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>8744.27</v>
+        <v>84500.77</v>
       </c>
       <c r="M17" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1640,28 +1637,28 @@
         <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
         <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I18">
-        <v>61671.520000000004</v>
+        <v>99341.3</v>
       </c>
       <c r="J18">
-        <v>5550.44</v>
+        <v>8940.72</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>67221.96</v>
+        <v>108282.02</v>
       </c>
       <c r="M18" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1669,40 +1666,40 @@
         <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
         <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I19">
-        <v>69219.88</v>
+        <v>1185.99</v>
       </c>
       <c r="J19">
+        <v>106.74</v>
+      </c>
+      <c r="K19">
         <v>0</v>
       </c>
-      <c r="K19">
-        <v>6229.79</v>
-      </c>
       <c r="L19">
-        <v>62990.09</v>
+        <v>1292.73</v>
       </c>
       <c r="M19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -1710,127 +1707,127 @@
         <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
         <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I20">
-        <v>30983.5</v>
+        <v>40840.9</v>
       </c>
       <c r="J20">
-        <v>2478.68</v>
+        <v>3675.68</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>33462.18</v>
+        <v>44516.58</v>
       </c>
       <c r="M20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="G21" t="s">
         <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I21">
-        <v>5406.76</v>
+        <v>86165.58</v>
       </c>
       <c r="J21">
-        <v>378.47</v>
+        <v>7754.9</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>5785.23</v>
+        <v>93920.48</v>
       </c>
       <c r="M21" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
         <v>120</v>
       </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" t="s">
-        <v>121</v>
-      </c>
       <c r="F22" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G22" t="s">
         <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22">
-        <v>86222.73999999999</v>
+        <v>36243.04</v>
       </c>
       <c r="J22">
-        <v>6035.59</v>
+        <v>2537.01</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>92258.33</v>
+        <v>38780.05</v>
       </c>
       <c r="M22" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
@@ -1842,7 +1839,7 @@
         <v>56</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
         <v>123</v>
@@ -1851,22 +1848,22 @@
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I23">
-        <v>60392.62</v>
+        <v>32675.24</v>
       </c>
       <c r="J23">
-        <v>4227.48</v>
+        <v>2940.77</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>64620.1</v>
+        <v>35616.01</v>
       </c>
       <c r="M23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -1874,40 +1871,40 @@
         <v>124</v>
       </c>
       <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
         <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>64</v>
       </c>
       <c r="E24" t="s">
         <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s">
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I24">
-        <v>52892.08</v>
+        <v>73041.49</v>
       </c>
       <c r="J24">
-        <v>4231.37</v>
+        <v>5112.9</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>57123.45</v>
+        <v>78154.39</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
@@ -1915,245 +1912,245 @@
         <v>126</v>
       </c>
       <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
       <c r="E25" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G25" t="s">
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I25">
-        <v>39698.85</v>
+        <v>6647.68</v>
       </c>
       <c r="J25">
-        <v>3175.91</v>
+        <v>598.29</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>42874.76</v>
+        <v>7245.97</v>
       </c>
       <c r="M25" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G26" t="s">
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I26">
-        <v>9476.28</v>
+        <v>24505.74</v>
       </c>
       <c r="J26">
-        <v>758.1</v>
+        <v>2205.52</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1715.4</v>
       </c>
       <c r="L26">
-        <v>10234.38</v>
+        <v>24995.86</v>
       </c>
       <c r="M26" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>81</v>
-      </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27">
-        <v>68246.75</v>
+        <v>8795.36</v>
       </c>
       <c r="J27">
-        <v>4777.27</v>
+        <v>615.68</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>175.91</v>
       </c>
       <c r="L27">
-        <v>73024.02</v>
+        <v>9235.13</v>
       </c>
       <c r="M27" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
         <v>85</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>86</v>
       </c>
-      <c r="D28" t="s">
-        <v>87</v>
-      </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
         <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I28">
-        <v>52485.57000000001</v>
+        <v>7799.76</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>545.98</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>52485.57</v>
+        <v>8345.74</v>
       </c>
       <c r="M28" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
         <v>91</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>92</v>
       </c>
-      <c r="D29" t="s">
-        <v>93</v>
-      </c>
       <c r="E29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G29" t="s">
         <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I29">
-        <v>9135.7</v>
+        <v>2566.97</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>205.36</v>
       </c>
       <c r="K29">
-        <v>456.79</v>
+        <v>154.02</v>
       </c>
       <c r="L29">
-        <v>8678.91</v>
+        <v>2618.31</v>
       </c>
       <c r="M29" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
         <v>98</v>
       </c>
-      <c r="C30" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" t="s">
-        <v>100</v>
-      </c>
       <c r="E30" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F30" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="G30" t="s">
         <v>19</v>
       </c>
       <c r="H30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I30">
-        <v>13539.56</v>
+        <v>57023.9</v>
       </c>
       <c r="J30">
-        <v>1218.56</v>
+        <v>5132.15</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>5132.15</v>
       </c>
       <c r="L30">
-        <v>14758.12</v>
+        <v>57023.9</v>
       </c>
       <c r="M30" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
@@ -2161,40 +2158,40 @@
         <v>143</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
         <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G31" t="s">
         <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I31">
-        <v>99859.05</v>
+        <v>65395.24</v>
       </c>
       <c r="J31">
-        <v>8987.31</v>
+        <v>5231.62</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>108846.36</v>
+        <v>70626.86</v>
       </c>
       <c r="M31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2205,7 +2202,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2219,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -2236,16 +2233,16 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>3323.32</v>
+        <v>2705.1</v>
       </c>
       <c r="E2">
-        <v>19939.92</v>
+        <v>13525.5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2253,50 +2250,50 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>128.98</v>
+        <v>293.49</v>
       </c>
       <c r="E3">
-        <v>386.94</v>
+        <v>1173.96</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>2525.84</v>
+        <v>4500.72</v>
       </c>
       <c r="E4">
-        <v>20206.72</v>
+        <v>45007.2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>1642.2</v>
+        <v>4021.86</v>
       </c>
       <c r="E5">
-        <v>4926.6</v>
+        <v>28153.02</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2304,16 +2301,16 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>4546.51</v>
+        <v>2185.17</v>
       </c>
       <c r="E6">
-        <v>13639.53</v>
+        <v>15296.19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2321,305 +2318,305 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>2462.65</v>
+        <v>4460.06</v>
       </c>
       <c r="E7">
-        <v>22163.85</v>
+        <v>22300.3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>2913.51</v>
+        <v>269.94</v>
       </c>
       <c r="E8">
-        <v>11654.04</v>
+        <v>2159.52</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>4693.95</v>
+        <v>3582.28</v>
       </c>
       <c r="E9">
-        <v>28163.7</v>
+        <v>25075.96</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>160.98</v>
+        <v>2617.44</v>
       </c>
       <c r="E10">
-        <v>482.94</v>
+        <v>2617.44</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>4595.96</v>
+        <v>2143.37</v>
       </c>
       <c r="E11">
-        <v>4595.96</v>
+        <v>10716.85</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>523.48</v>
+        <v>2869.95</v>
       </c>
       <c r="E12">
-        <v>4711.32</v>
+        <v>11479.8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>2710.56</v>
+        <v>4660.78</v>
       </c>
       <c r="E13">
-        <v>18973.92</v>
+        <v>9321.56</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>1867.58</v>
+        <v>1066.9</v>
       </c>
       <c r="E14">
-        <v>3735.16</v>
+        <v>7468.3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1534.91</v>
+        <v>1256.47</v>
       </c>
       <c r="E15">
-        <v>4604.73</v>
+        <v>2512.94</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>2821.37</v>
+        <v>154.73</v>
       </c>
       <c r="E16">
-        <v>25392.33</v>
+        <v>464.19</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>4977.57</v>
+        <v>2513.98</v>
       </c>
       <c r="E17">
-        <v>44798.13</v>
+        <v>20111.84</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>2593.45</v>
+        <v>2415.5</v>
       </c>
       <c r="E18">
-        <v>2593.45</v>
+        <v>19324</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>1113.08</v>
+        <v>1247.65</v>
       </c>
       <c r="E19">
-        <v>2226.16</v>
+        <v>7485.9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>2249.82</v>
+        <v>3977.17</v>
       </c>
       <c r="E20">
-        <v>11249.1</v>
+        <v>3977.17</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>679.02</v>
+        <v>2316.59</v>
       </c>
       <c r="E21">
-        <v>5432.16</v>
+        <v>13899.54</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>4321.58</v>
+        <v>2536.03</v>
       </c>
       <c r="E22">
-        <v>4321.58</v>
+        <v>12680.15</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>1438.47</v>
+        <v>1066.48</v>
       </c>
       <c r="E23">
-        <v>7192.35</v>
+        <v>6398.88</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>3807.82</v>
+        <v>3764.03</v>
       </c>
       <c r="E24">
-        <v>15231.28</v>
+        <v>33876.27</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2627,16 +2624,16 @@
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>1900.51</v>
+        <v>1547.84</v>
       </c>
       <c r="E25">
-        <v>13303.57</v>
+        <v>15478.4</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2644,16 +2641,16 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>2685.06</v>
+        <v>4318.16</v>
       </c>
       <c r="E26">
-        <v>8055.18</v>
+        <v>17272.64</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2661,441 +2658,441 @@
         <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>3433.23</v>
+        <v>1537.91</v>
       </c>
       <c r="E27">
-        <v>24032.61</v>
+        <v>3075.82</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>217.85</v>
+        <v>1956.46</v>
       </c>
       <c r="E28">
-        <v>1089.25</v>
+        <v>17608.14</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>1769.39</v>
+        <v>4696.88</v>
       </c>
       <c r="E29">
-        <v>8846.95</v>
+        <v>42271.92</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>3405.46</v>
+        <v>2370.89</v>
       </c>
       <c r="E30">
-        <v>17027.3</v>
+        <v>14225.34</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>172.87</v>
+        <v>1318.17</v>
       </c>
       <c r="E31">
-        <v>691.48</v>
+        <v>1318.17</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32">
-        <v>2933.41</v>
+        <v>258.53</v>
       </c>
       <c r="E32">
-        <v>17600.46</v>
+        <v>2068.24</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>1862.39</v>
+        <v>2383.88</v>
       </c>
       <c r="E33">
-        <v>7449.56</v>
+        <v>4767.76</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34">
-        <v>807.01</v>
+        <v>2927.09</v>
       </c>
       <c r="E34">
-        <v>1614.02</v>
+        <v>5854.18</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35">
-        <v>1761.04</v>
+        <v>938.27</v>
       </c>
       <c r="E35">
-        <v>5283.12</v>
+        <v>2814.81</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>3376.92</v>
+        <v>2344.52</v>
       </c>
       <c r="E36">
-        <v>3376.92</v>
+        <v>16411.64</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>3466.07</v>
+        <v>1554.81</v>
       </c>
       <c r="E37">
-        <v>13864.28</v>
+        <v>9328.86</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C38">
         <v>7</v>
       </c>
       <c r="D38">
-        <v>3657.35</v>
+        <v>1598.64</v>
       </c>
       <c r="E38">
-        <v>25601.45</v>
+        <v>11190.48</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D39">
-        <v>4153.46</v>
+        <v>2646.08</v>
       </c>
       <c r="E39">
-        <v>37381.14</v>
+        <v>5292.16</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40">
-        <v>3509.59</v>
+        <v>4291.6</v>
       </c>
       <c r="E40">
-        <v>14038.36</v>
+        <v>17166.4</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>724.2</v>
+        <v>1241.4</v>
       </c>
       <c r="E41">
-        <v>5069.4</v>
+        <v>2482.8</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42">
-        <v>889.43</v>
+        <v>4136.84</v>
       </c>
       <c r="E42">
-        <v>8004.87</v>
+        <v>28957.88</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D43">
-        <v>1378.79</v>
+        <v>498.22</v>
       </c>
       <c r="E43">
-        <v>4136.37</v>
+        <v>2989.32</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>979.67</v>
+        <v>3000.86</v>
       </c>
       <c r="E44">
-        <v>979.67</v>
+        <v>15004.3</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>3148.79</v>
+        <v>4900.3</v>
       </c>
       <c r="E45">
-        <v>15743.95</v>
+        <v>49003</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D46">
-        <v>2351.66</v>
+        <v>659.73</v>
       </c>
       <c r="E46">
-        <v>2351.66</v>
+        <v>5937.57</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D47">
-        <v>968.63</v>
+        <v>3489.37</v>
       </c>
       <c r="E47">
-        <v>3874.52</v>
+        <v>24425.59</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D48">
-        <v>3556.34</v>
+        <v>2572.17</v>
       </c>
       <c r="E48">
-        <v>24894.38</v>
+        <v>23149.53</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D49">
-        <v>4000.62</v>
+        <v>4071.45</v>
       </c>
       <c r="E49">
-        <v>36005.58</v>
+        <v>20357.25</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>2635.06</v>
+        <v>3313.68</v>
       </c>
       <c r="E50">
-        <v>5270.12</v>
+        <v>16568.4</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51">
-        <v>2370.96</v>
+        <v>2944.33</v>
       </c>
       <c r="E51">
-        <v>7112.88</v>
+        <v>17665.98</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C52">
         <v>7</v>
       </c>
       <c r="D52">
-        <v>1156.65</v>
+        <v>4512.83</v>
       </c>
       <c r="E52">
-        <v>8096.55</v>
+        <v>31589.81</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3103,16 +3100,16 @@
         <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>2907.08</v>
+        <v>1601.16</v>
       </c>
       <c r="E53">
-        <v>26163.72</v>
+        <v>11208.12</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3120,866 +3117,577 @@
         <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D54">
-        <v>1617.26</v>
+        <v>4319.71</v>
       </c>
       <c r="E54">
-        <v>16172.6</v>
+        <v>38877.39</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>1933.52</v>
+        <v>1185.99</v>
       </c>
       <c r="E55">
-        <v>19335.2</v>
+        <v>1185.99</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56">
-        <v>431.11</v>
+        <v>207.69</v>
       </c>
       <c r="E56">
-        <v>4311.1</v>
+        <v>1661.52</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D57">
-        <v>4601.53</v>
+        <v>3756.88</v>
       </c>
       <c r="E57">
-        <v>32210.71</v>
+        <v>15027.52</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58">
-        <v>4104.06</v>
+        <v>4025.31</v>
       </c>
       <c r="E58">
-        <v>8208.12</v>
+        <v>24151.86</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D59">
-        <v>1906.34</v>
+        <v>2603.99</v>
       </c>
       <c r="E59">
-        <v>1906.34</v>
+        <v>18227.93</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D60">
-        <v>3226.23</v>
+        <v>275.27</v>
       </c>
       <c r="E60">
-        <v>22583.61</v>
+        <v>825.81</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D61">
-        <v>3561.93</v>
+        <v>4911.77</v>
       </c>
       <c r="E61">
-        <v>3561.93</v>
+        <v>34382.39</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D62">
-        <v>3066.07</v>
+        <v>3294.59</v>
       </c>
       <c r="E62">
-        <v>18396.42</v>
+        <v>29651.31</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B63" t="s">
         <v>159</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>786.21</v>
+        <v>1539.07</v>
       </c>
       <c r="E63">
-        <v>2358.63</v>
+        <v>3078.14</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D64">
-        <v>3333.26</v>
+        <v>4530.38</v>
       </c>
       <c r="E64">
-        <v>6666.52</v>
+        <v>36243.04</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D65">
-        <v>186</v>
+        <v>1195.46</v>
       </c>
       <c r="E65">
-        <v>1860</v>
+        <v>4781.84</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>3546.76</v>
+        <v>4648.9</v>
       </c>
       <c r="E66">
-        <v>3546.76</v>
+        <v>27893.4</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C67">
         <v>6</v>
       </c>
       <c r="D67">
-        <v>1445.76</v>
+        <v>4612.95</v>
       </c>
       <c r="E67">
-        <v>8674.56</v>
+        <v>27677.7</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D68">
-        <v>3205.06</v>
+        <v>1607.67</v>
       </c>
       <c r="E68">
-        <v>12820.24</v>
+        <v>11253.69</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B69" t="s">
         <v>158</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>2708.92</v>
+        <v>532.88</v>
       </c>
       <c r="E69">
-        <v>8126.76</v>
+        <v>532.88</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C70">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D70">
-        <v>2287.42</v>
+        <v>1827.17</v>
       </c>
       <c r="E70">
-        <v>20586.78</v>
+        <v>18271.7</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71">
-        <v>4001.6</v>
+        <v>1913.19</v>
       </c>
       <c r="E71">
-        <v>36014.4</v>
+        <v>15305.52</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C72">
         <v>4</v>
       </c>
       <c r="D72">
-        <v>2303.65</v>
+        <v>1661.92</v>
       </c>
       <c r="E72">
-        <v>9214.6</v>
+        <v>6647.68</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>3914.54</v>
+        <v>4711.94</v>
       </c>
       <c r="E73">
-        <v>15658.16</v>
+        <v>23559.7</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>186.11</v>
+        <v>203.22</v>
       </c>
       <c r="E74">
-        <v>1302.77</v>
+        <v>203.22</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>3817.91</v>
+        <v>371.41</v>
       </c>
       <c r="E75">
-        <v>26725.37</v>
+        <v>742.82</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D76">
-        <v>1248.62</v>
+        <v>1256.48</v>
       </c>
       <c r="E76">
-        <v>7491.72</v>
+        <v>8795.36</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C77">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>1499.41</v>
+        <v>2599.92</v>
       </c>
       <c r="E77">
-        <v>14994.1</v>
+        <v>7799.76</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D78">
-        <v>3891</v>
+        <v>366.71</v>
       </c>
       <c r="E78">
-        <v>7782</v>
+        <v>2566.97</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
         <v>159</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>3372.99</v>
+        <v>539.19</v>
       </c>
       <c r="E79">
-        <v>16864.95</v>
+        <v>1078.38</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D80">
-        <v>4417.01</v>
+        <v>4429.71</v>
       </c>
       <c r="E80">
-        <v>13251.03</v>
+        <v>22148.55</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B81" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C81">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D81">
-        <v>3350.65</v>
+        <v>749.17</v>
       </c>
       <c r="E81">
-        <v>26805.2</v>
+        <v>6742.53</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D82">
-        <v>3030.64</v>
+        <v>476.63</v>
       </c>
       <c r="E82">
-        <v>3030.64</v>
+        <v>3813.04</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D83">
-        <v>4579.92</v>
+        <v>3320.2</v>
       </c>
       <c r="E83">
-        <v>9159.84</v>
+        <v>23241.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D84">
-        <v>234.39</v>
+        <v>2217.77</v>
       </c>
       <c r="E84">
-        <v>703.17</v>
+        <v>17742.16</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B85" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D85">
-        <v>691.57</v>
+        <v>206.31</v>
       </c>
       <c r="E85">
-        <v>2766.28</v>
+        <v>1237.86</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C86">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D86">
-        <v>1677.5</v>
+        <v>4646.91</v>
       </c>
       <c r="E86">
-        <v>6710</v>
+        <v>32528.37</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C87">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D87">
-        <v>2231.83</v>
+        <v>4628.95</v>
       </c>
       <c r="E87">
-        <v>20086.47</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>131</v>
-      </c>
-      <c r="B88" t="s">
-        <v>172</v>
-      </c>
-      <c r="C88">
-        <v>3</v>
-      </c>
-      <c r="D88">
-        <v>4436.64</v>
-      </c>
-      <c r="E88">
-        <v>13309.92</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>131</v>
-      </c>
-      <c r="B89" t="s">
-        <v>159</v>
-      </c>
-      <c r="C89">
-        <v>6</v>
-      </c>
-      <c r="D89">
-        <v>990.61</v>
-      </c>
-      <c r="E89">
-        <v>5943.66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>131</v>
-      </c>
-      <c r="B90" t="s">
-        <v>166</v>
-      </c>
-      <c r="C90">
-        <v>8</v>
-      </c>
-      <c r="D90">
-        <v>1315.8</v>
-      </c>
-      <c r="E90">
-        <v>10526.4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>131</v>
-      </c>
-      <c r="B91" t="s">
-        <v>150</v>
-      </c>
-      <c r="C91">
-        <v>5</v>
-      </c>
-      <c r="D91">
-        <v>3676.06</v>
-      </c>
-      <c r="E91">
-        <v>18380.3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>134</v>
-      </c>
-      <c r="B92" t="s">
-        <v>163</v>
-      </c>
-      <c r="C92">
-        <v>3</v>
-      </c>
-      <c r="D92">
-        <v>2393.48</v>
-      </c>
-      <c r="E92">
-        <v>7180.44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>134</v>
-      </c>
-      <c r="B93" t="s">
-        <v>151</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93">
-        <v>3565.72</v>
-      </c>
-      <c r="E93">
-        <v>7131.44</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>134</v>
-      </c>
-      <c r="B94" t="s">
-        <v>165</v>
-      </c>
-      <c r="C94">
-        <v>6</v>
-      </c>
-      <c r="D94">
-        <v>535.47</v>
-      </c>
-      <c r="E94">
-        <v>3212.82</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>134</v>
-      </c>
-      <c r="B95" t="s">
-        <v>149</v>
-      </c>
-      <c r="C95">
-        <v>7</v>
-      </c>
-      <c r="D95">
-        <v>4994.41</v>
-      </c>
-      <c r="E95">
-        <v>34960.87</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>137</v>
-      </c>
-      <c r="B96" t="s">
-        <v>169</v>
-      </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>3574.56</v>
-      </c>
-      <c r="E96">
-        <v>3574.56</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>137</v>
-      </c>
-      <c r="B97" t="s">
-        <v>158</v>
-      </c>
-      <c r="C97">
-        <v>4</v>
-      </c>
-      <c r="D97">
-        <v>702.16</v>
-      </c>
-      <c r="E97">
-        <v>2808.64</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>137</v>
-      </c>
-      <c r="B98" t="s">
-        <v>165</v>
-      </c>
-      <c r="C98">
-        <v>6</v>
-      </c>
-      <c r="D98">
-        <v>458.75</v>
-      </c>
-      <c r="E98">
-        <v>2752.5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>140</v>
-      </c>
-      <c r="B99" t="s">
-        <v>154</v>
-      </c>
-      <c r="C99">
-        <v>5</v>
-      </c>
-      <c r="D99">
-        <v>1864.96</v>
-      </c>
-      <c r="E99">
-        <v>9324.8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>140</v>
-      </c>
-      <c r="B100" t="s">
-        <v>151</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100">
-        <v>4214.76</v>
-      </c>
-      <c r="E100">
-        <v>4214.76</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>143</v>
-      </c>
-      <c r="B101" t="s">
-        <v>167</v>
-      </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
-      <c r="D101">
-        <v>2037.87</v>
-      </c>
-      <c r="E101">
-        <v>6113.61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>143</v>
-      </c>
-      <c r="B102" t="s">
-        <v>162</v>
-      </c>
-      <c r="C102">
-        <v>6</v>
-      </c>
-      <c r="D102">
-        <v>1946.09</v>
-      </c>
-      <c r="E102">
-        <v>11676.54</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>143</v>
-      </c>
-      <c r="B103" t="s">
-        <v>155</v>
-      </c>
-      <c r="C103">
-        <v>10</v>
-      </c>
-      <c r="D103">
-        <v>4724.86</v>
-      </c>
-      <c r="E103">
-        <v>47248.6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>143</v>
-      </c>
-      <c r="B104" t="s">
-        <v>166</v>
-      </c>
-      <c r="C104">
-        <v>10</v>
-      </c>
-      <c r="D104">
-        <v>3482.03</v>
-      </c>
-      <c r="E104">
-        <v>34820.3</v>
+        <v>13886.85</v>
       </c>
     </row>
   </sheetData>
